--- a/artfynd/A 9309-2023 artfynd.xlsx
+++ b/artfynd/A 9309-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9309-2023 artfynd.xlsx
+++ b/artfynd/A 9309-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>4823771</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523623.945423548</v>
+        <v>523624</v>
       </c>
       <c r="R2" t="n">
-        <v>6234882.738783617</v>
+        <v>6234883</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2013-05-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-05-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -809,12 +794,7 @@
         <v>4823772</v>
       </c>
       <c r="B3" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -855,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523629.3599201888</v>
+        <v>523629</v>
       </c>
       <c r="R3" t="n">
-        <v>6234909.982096558</v>
+        <v>6234910</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,19 +868,9 @@
           <t>2013-05-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-05-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
